--- a/public/dropvine-cost-calculator.xlsx
+++ b/public/dropvine-cost-calculator.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
-    <t xml:space="preserve">🧮  Cost Calculator</t>
+    <t xml:space="preserve">Cost Calculator</t>
   </si>
   <si>
     <t xml:space="preserve">Break down the real cost of what you make — ingredient by ingredient — by Dropvine</t>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">For each ingredient or material, enter what you paid for the whole package and how much the package contains.</t>
+    <t xml:space="preserve">For each ingredient or material, enter what you paid for the whole package and how much it contains.</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">4</t>
   </si>
   <si>
-    <t xml:space="preserve">Your cost per ingredient fills in automatically. The total at the bottom is your cost per product.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">💡  Use this to find your true cost-per-unit — then plug that number into the Pricing Calculator to figure out what to charge.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">🌱  Use alongside the Pricing Calculator · Built by Dropvine — dropvine.pro</t>
+    <t xml:space="preserve">Your cost per ingredient fills in automatically. The total is your cost per product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use this to find your true cost-per-unit — then plug that number into the Pricing Calculator to figure out what to charge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use alongside the Pricing Calculator · Built by Dropvine — dropvine.pro</t>
   </si>
   <si>
     <t xml:space="preserve">Product name:</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">Sourdough starter</t>
   </si>
   <si>
-    <t xml:space="preserve">→  TOTAL COST PER ITEM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Take the total cost per item and plug it into the Pricing Calculator as your ingredient/material cost.  🌱  Dropvine — dropvine.pro</t>
+    <t xml:space="preserve">TOTAL COST PER ITEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Take the total cost per item and plug it into the Pricing Calculator as your ingredient/material cost.  Built by Dropvine — dropvine.pro</t>
   </si>
 </sst>
 </file>
@@ -712,148 +712,148 @@
       <c r="G4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>5</v>
-      </c>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
@@ -864,19 +864,19 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
@@ -885,13 +885,13 @@
       <c r="G21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
@@ -903,24 +903,24 @@
       <c r="G23" s="1"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="A24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
@@ -1239,18 +1239,18 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A2:G5"/>
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:G9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:G12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:G15"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:G18"/>
-    <mergeCell ref="A21:G22"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A2:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:G8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:G11"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:G14"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:G17"/>
+    <mergeCell ref="A20:G21"/>
+    <mergeCell ref="A24:G24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
